--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-average.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-average.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{451DC665-3CEF-4C04-867A-D6A28261B299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70072FAA-98C5-4BB0-BCB1-6349897EECC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{5785F219-7A99-479B-AA98-A923E69E47C3}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{D313BBE2-6CDA-487E-B439-62B10E9BA8D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576869560187" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{D65967A8-BDA4-4BC7-93C2-E65753C4C743}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579431134262" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{67787A86-53B9-456F-BA93-BFB4F10274E4}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{066BE52C-C233-4FF3-A5AA-A5285DB347E9}" name="AllErrorPivot" cacheId="71" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD56C29E-146A-46AA-A1E2-83636F44AD68}" name="AllErrorPivot" cacheId="71" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -531,7 +531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAE1D30-9551-4617-9996-4D2909C1F115}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA41F374-3758-4A54-95FF-6AFD5869A923}">
   <dimension ref="A4:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7AEBAC-FA22-4E5D-B8B2-D97F7CC9E8D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C11831D-524C-48B2-AD8E-B9263854D685}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
